--- a/data/raw/inventory/Week 34/Audio_Array/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 34/Audio_Array/Inventory Snapshot.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\Audio Array\Week 33\Week 33\Inventory\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 34\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A3D53C-9632-4BF5-A78B-3C92E0165C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
